--- a/Model_Navigate/TXresearch/腾讯研究院文章列表.xlsx
+++ b/Model_Navigate/TXresearch/腾讯研究院文章列表.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -525,20 +525,20 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>首次付费是AI消费爆发的引爆点 | T-ask调研
-AI大模型付费用户中62.8%计划增加硬件消费，是非用户（10.1%）的6倍以上；AI硬件用户中33.8%计划增加大模型消费，是非硬件用户（10.9%）的3倍以上。在已购买或使用过AI硬件的用户中，33.8%…</t>
+          <t>那些跑通 AI 变革的团队做对了什么？
+胡一川：对，所以今天我发现，人越少的团队效率越高——他们没有那么多人的沟通，可能就是每天早上两三个人开半小时的会，把最重要的事情讨论决策，然后各自去干，让AI去干。王若愚：对，因为特别现实的一个点是：在座各位…</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>https://www.sohu.com/a/1021615161_455313?scm=10001.325_13-325_13.0.0-0-0-0-0.5_1334&amp;spm=smpc.channel_248.block3_308_NDdFbm_1_fd.2.1778644257183mMjRSDr_324</t>
+          <t>https://www.sohu.com/a/1034841678_455313?scm=10001.325_13-325_13.0.0-0-0-0-0.5_1334&amp;spm=smpc.channel_248.block3_308_NDdFbm_1_fd.2.1781151373534udvtkO8_324</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>335</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -553,24 +553,20 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>腾讯研究院AI速递 20260512
-AI能力呈"超指数级"增长，Mythos表现已超过2027年AGI预测线，从2021年8秒任务到2026年16小时任务，每代跃升幅度更大、间隔更短；伟大的公司本质是组织发明，竞争的不只是市场或薪酬而是身份认同…</t>
+          <t>AI时代，一种新经济正在长出来｜智联网·价值篇
+如果AI只是做了一个简单的路由（把客户转接给人类），它不收或者只收极低的流量费；只有当AI独立、完整地帮客户解决了问题（比如成功办理了退款、修改了订单、挽留了退订），它才会收取一笔解决费，通常在每单1到1.5…</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>https://www.sohu.com/a/1021256514_455313?scm=10001.325_13-325_13.0.0-0-0-0-0.5_1334&amp;spm=smpc.channel_248.block3_308_NDdFbm_1_fd.3.1778644257183mMjRSDr_324</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
+          <t>https://www.sohu.com/a/1034323050_455313?scm=10001.325_13-325_13.0.0-0-0-0-0.5_1334&amp;spm=smpc.channel_248.block3_308_NDdFbm_1_fd.4.1781151373534udvtkO8_324</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>307</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -585,20 +581,20 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>我们刚过了人类最后一个劳动节？AI新职业的八个变化
-研究的核心框架，是把AI公司的全部在招岗位归成五类——使能者（做模型）、协作者（做产品和交付）、推广者（做销售和营销）、治理者（管安全和合规）、支持者（管后勤和运营），以消除各家公司岗位差异性较大的问题，便于…</t>
+          <t>人人都聊未来产业，无人关心未来社会
+并非没有人讨论——许多研究报告涉及了“人机社会”“未来社区”“生成式社会学”等前沿概念；国际学界中，AI与社会不平等、算法权力、老龄化照护等议题也在升温。本文所说的“未来社会”，不是乌托邦蓝图，也不是哲学意义…</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>https://www.sohu.com/a/1021120980_455313?scm=10001.325_13-325_13.0.0-0-0-0-0.5_1334&amp;spm=smpc.channel_248.block3_308_NDdFbm_1_fd.4.1778644257183mMjRSDr_324</t>
+          <t>https://www.sohu.com/a/1033817551_455313?scm=10001.325_13-325_13.0.0-0-0-0-0.5_1334&amp;spm=smpc.channel_248.block3_308_NDdFbm_1_fd.6.1781151373534udvtkO8_324</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>870</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -613,24 +609,24 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>腾讯研究院AI速递 20260511
-数据策略从遥操作转向第一视角视频，英伟达EgoScale项目用2.1万小时人类视频预训练，实现22自由度机器人手的端到端策略；提出文明科技树三大成就：通过物理图灵测试约2-3年、物理API实现自动化制造、物理…</t>
+          <t>腾讯研究院AI速递 20260608
+Anthropic发长文披露Claude正加速AI发展，疑似递归自我提升（RSI）路径：截至5月超80%代码由Claude编写，工程师季度交付量是2021-2025年的8倍，开放编程任务成功率半年内从26%跃…</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>https://www.sohu.com/a/1020787830_455313?scm=10001.325_13-325_13.0.0-0-0-0-0.5_1334&amp;spm=smpc.channel_248.block3_308_NDdFbm_1_fd.5.1778644257183mMjRSDr_324</t>
+          <t>https://www.sohu.com/a/1033484517_455313?scm=10001.325_13-325_13.0.0-0-0-0-0.5_1334&amp;spm=smpc.channel_248.block3_308_NDdFbm_1_fd.7.1781151373534udvtkO8_324</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>333</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -645,20 +641,20 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>腾讯研究院AI每周关键词Top50
-AI前沿每周关键词Top50（0427-0509）每周50关键词把握全局AI动态英伟达等DeepMind等EpochAI等a16z等Anthropic等OpenAI等👇扫码加入AGI数据库，AI智能问答（腾…</t>
+          <t>万字实录现场直出：汤道生、姚顺雨对谈腾讯 AI 下半场
+好的产品能够解决第一个问题：我们做预训练和后训练之后到底要把它应用在什么地方产生价值；第二个是环境是非常重要的，如果没有好的环境，那Agent没有办法做各种各样的事情，比如说如果没有一个点外卖的tool的话，…</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>https://www.sohu.com/a/1020562231_455313?scm=10001.325_13-325_13.0.0-0-0-0-0.5_1334&amp;spm=smpc.channel_248.block3_308_NDdFbm_1_fd.6.1778644257183mMjRSDr_324</t>
+          <t>https://www.sohu.com/a/1032560716_455313?scm=10001.325_13-325_13.0.0-0-0-0-0.5_1334&amp;spm=smpc.channel_248.block3_308_NDdFbm_1_fd.8.1781151373534udvtkO8_324</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>545</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -673,24 +669,24 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>腾讯研究院AI速递 20260509
-OpenAI在API中推出GPT-Realtime-2、GPT-Realtime-Translate、GPT-Realtime-Whisper三款新模型，覆盖推理、翻译与转录场景；OpenAI发布Codex的…</t>
+          <t>腾讯研究院AI速递 20260605
+谷歌推出Gemma412B，把多模态智能体能力带到笔记本，介于边缘端E4B与26BMoE之间，仅需16GB显存即可本地运行，是谷歌首个支持原生音频输入的中等规模模型；新增工作板支持多智能体编排协同，主智能体可…</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>https://www.sohu.com/a/1020046836_455313?scm=10001.325_13-325_13.0.0-0-0-0-0.5_1334&amp;spm=smpc.channel_248.block3_308_NDdFbm_1_fd.7.1778644257183mMjRSDr_324</t>
+          <t>https://www.sohu.com/a/1032305007_455313?scm=10001.325_13-325_13.0.0-0-0-0-0.5_1334&amp;spm=smpc.channel_248.block3_308_NDdFbm_1_fd.9.1781151373534udvtkO8_324</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>415</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -705,20 +701,20 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>AGI 之路，可能从一开始就走错了
-这篇文章想把一个很多人隐约感觉到但没说透的判断讲出来：我们现在所走的这条所谓"通往AGI"的大模型路线，极有可能从一开始就走错了。奥特曼和马斯克这两年频繁谈"核聚变"和"太空数据中心"——不是情怀，是因为地球…</t>
+          <t>Token必须死？
+2026年5月，MIT何恺明团队和字节跳动Seed实验室几乎同时发布论文，给出了一个更明确的信号：语言生成的核心建模过程不必始终发生在离散token空间中，也可以转移到连续embedding或latent空间…</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>https://www.sohu.com/a/1019888718_455313?scm=10001.325_13-325_13.0.0-0-0-0-0.5_1334&amp;spm=smpc.channel_248.block3_308_NDdFbm_1_fd.8.1778644257183mMjRSDr_324</t>
+          <t>https://www.sohu.com/a/1032206614_455313?scm=10001.325_13-325_13.0.0-0-0-0-0.5_1334&amp;spm=smpc.channel_248.block3_308_NDdFbm_1_fd.10.1781151373534udvtkO8_324</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>299</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -733,20 +729,24 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>注定改变历史的一代人
-当算法可以完成越来越多的"有用"工作，当人类在认知、情感、社会层面都面临算法的挑战，AI原生代可能面临一个更根本的问题，在算法时代，人类的意义是什么？但AI时代可能不同，因为这次挑战的不是某一项技能或某一种职…</t>
+          <t>腾讯研究院AI速递 20260604
+架构分三层：Nemotron3Super模型负责推理，Hermes管理技能与记忆，OpenShell负责沙箱隔离，可全本地运行并接入Slack、Outlook、GitHub等数据源；KimiWork是面向知识…</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>https://www.sohu.com/a/1019405291_455313?scm=10001.325_13-325_13.0.0-0-0-0-0.5_1334&amp;spm=smpc.channel_248.block3_308_NDdFbm_1_fd.10.1778644257183mMjRSDr_324</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr"/>
+          <t>https://www.sohu.com/a/1031800192_455313?scm=10001.325_13-325_13.0.0-0-0-0-0.5_1334&amp;spm=smpc.channel_248.block3_308_NDdFbm_1_fd.11.1781151373534udvtkO8_324</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>306</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -761,23 +761,287 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>范凌：当公司变成Agent，关于 AI 时代组织的 5 个反思
-第二刀是在pod之外建community：横向社区帮所有人补齐销售、产品、代码等跨界能力，并专设Leadershipcommunity——范凌判断，AI时代带100个Agent比带10个人更难，podlead…</t>
+          <t>超级个体时代｜腾讯研究院3万字报告
+在美图，CEO吴欣鸿提出了超级设计师的概念，内部已经出现了多个跨越岗位边界的案例：RoboNeo的产品负责人原来是设计师，自学了模型部署和AI编程，现在很难定义他到底是设计师、产品经理还是工程师；一位原本只跟…</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>https://www.sohu.com/a/1018984466_455313?scm=10001.325_13-325_13.0.0-0-0-0-0.5_1334&amp;spm=smpc.channel_248.block3_308_NDdFbm_1_fd.12.1778644257183mMjRSDr_324</t>
+          <t>https://www.sohu.com/a/1031722997_455313?scm=10001.325_13-325_13.0.0-0-0-0-0.5_1334&amp;spm=smpc.channel_248.block3_308_NDdFbm_1_fd.12.1781151373534udvtkO8_324</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1446</t>
+          <t>1702</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递 20260603
+纯文本能力接近旗舰Qwen3.7-Max，编程、Agent、推理及视觉推理多项评测显著提升，支持工具调用与GUI感知操控。真正的AI-Native组织需默认信任与平等主义两大前提，AI能力向每个人开放、对话全…</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sohu.com/a/1031284510_455313?scm=10001.325_13-325_13.0.0-0-0-0-0.5_1334&amp;spm=smpc.channel_248.block3_308_NDdFbm_1_fd.13.1781151373534udvtkO8_324</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>什么可以抵消全球老龄化的影响？
+自动化和人工智能，更高的老年人口劳动参与率，以及印度和非洲人口友好型经济体的发展前景，是我们最常听到的抵消老龄化影响的因素。一些非洲经济体的营商便利度得分确实比印度高，少数得分甚至比中国还高，然而，非洲存在两…</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sohu.com/a/1031150316_455313?scm=10001.325_13-325_13.0.0-0-0-0-0.5_1334&amp;spm=smpc.channel_248.block3_308_NDdFbm_1_fd.14.1781151373534udvtkO8_324</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递 20260602
+针对当前世界模型本质仍是视频预测器、缺乏独立世界状态的局限，VAST提出将状态推演与视觉呈现原生解耦的三层架构技术路线；参考平台把行业最难最重复的基础集成工作做完，让团队站在标准化底座上创新，标志人形机器人从…</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sohu.com/a/1030856562_455313?scm=10001.325_13-325_13.0.0-0-0-0-0.5_1334&amp;spm=smpc.channel_248.block3_308_NDdFbm_1_fd.15.1781151373534udvtkO8_324</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>一个理想的组织，是AI Agent在组织人｜AI跃迁者调研
+我们每期会邀请一位AI跃迁者，可能是AI原生创业者，可能是正在用AI重做组织的一号位，也可能是把自己作为AIFirst实验的超级个体，分享他们想清楚的结论、拆过的过程、建出来的东西、交过的学费，以及在持续变化…</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sohu.com/a/1030698961_455313?scm=10001.325_13-325_13.0.0-0-0-0-0.5_1334&amp;spm=smpc.channel_248.block3_308_NDdFbm_1_fd.16.1781151373534udvtkO8_324</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递 20260601
+北大数院"黄金二代"苏炜杰官宣加入OpenAI并晋升沃顿正教授，将从统计与优化理论直接参与模型训练，OpenAI联创Brockman发帖欢迎；前SalesforceAI研究负责人创办的actAVA发布CHIB…</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sohu.com/a/1030288132_455313?scm=10001.325_13-325_13.0.0-0-0-0-0.5_1334&amp;spm=smpc.channel_248.block3_308_NDdFbm_1_fd.17.1781151373534udvtkO8_324</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>439</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>AI为什么会“失语”？
+研究者扫描了GPT-2、Llama、Mistral等一批主流开源模型的词表，所谓词表，就是模型在读字之前预先编好的一张固定清单，把所有可能用到的字符组合都列进去，每一项叫一个token，模型说出的每一个字都必…</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sohu.com/a/1029435323_455313?scm=10001.325_13-325_13.0.0-0-0-0-0.5_1334&amp;spm=smpc.channel_248.block3_308_NDdFbm_1_fd.18.1781151373534udvtkO8_324</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>889</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>AI破晓：生成式AI时代文化产业的重塑、跃迁与守望｜4万字报告
+文化产业的从业者、研究者、治理者都在追问与思考：生成式AI时代，文化产业的新范式、新秩序、新价值、新生态将会发生怎样的变化；而又有哪些底层逻辑和基本规律，会穿越时间之河长存于世；我们又当如何做出更为积极主动的…</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sohu.com/a/1028965373_455313?scm=10001.325_13-325_13.0.0-0-0-0-0.5_1334&amp;spm=smpc.channel_248.block3_308_NDdFbm_1_fd.20.1781151373534udvtkO8_324</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>AI商业化的十字路口：为什么广告与订阅都难以单独走通？
+ChatGPT拥有接近10亿的周活跃用户规模，并早在2022年底就火爆出圈，其商业化路径更接近传统互联网公司的“入口+流量逻辑”：先通过ChatGPT建立最大规模的通用用户入口，再在搜索、办公、购物、开发者工…</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sohu.com/a/1028463953_455313?scm=10001.325_13-325_13.0.0-1-0-0-0.5_1334&amp;spm=smpc.channel_248.block3_308_NDdFbm_1_fd.22.1781151373534udvtkO8_324</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>NOVA：全国人工智能创意挑战赛正式启动
+适逢香港科技大学成立35周年，腾讯研究院联合香港科技大学商学院技术与商业生态研究中心、香港科技大学上海校友会，共同推出“NOVA：全国人工智能创意挑战赛”，面向香港与内地的大学生与高中生招募优秀AI创意团队。…</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>https://www.sohu.com/a/1028456245_455313?scm=10001.325_13-325_13.0.0-1-0-0-0.5_1334&amp;spm=smpc.channel_248.block3_308_NDdFbm_1_fd.23.1781151373534udvtkO8_324</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>449</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -794,6 +1058,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
